--- a/demo/asteria/sources/governance/risk_register.xlsx
+++ b/demo/asteria/sources/governance/risk_register.xlsx
@@ -430,6 +430,636 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AST-R-SLA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Contractual service commitment missed without detection</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AST-R-SEG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Segregation of duties conflict in a financial process</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AST-R-BACKUP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Backups are not restorable when needed</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AST-R-KEY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cryptographic key exposure or loss</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AST-R-VULN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Known vulnerability remains unpatched beyond policy</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AST-R-LOG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Security-relevant activity is not logged or is alterable</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AST-R-SDLC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Defect reaches production through inadequate testing</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AST-R-TAX</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Indirect tax is misdeclared across jurisdictions</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AST-R-PAYROLL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Payroll is paid to a person who has left</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>chro@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AST-R-CONTRACT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>An executed contract term is not operationalised</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>gc@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AST-R-AML</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Counterparty screening fails to identify a sanctioned party</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>gc@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AST-R-CONC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Revenue concentration in a single customer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ceo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AST-R-KEYPERSON</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Loss of a single engineer with undocumented knowledge</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AST-R-AI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>An automated decision is relied on without human review</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AST-R-PHYS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Unauthorised physical access to the Paris office</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>coo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>